--- a/Sufficient data WITH_PO/forecast_summary_B083NMK4BB_WITH_PO.xlsx
+++ b/Sufficient data WITH_PO/forecast_summary_B083NMK4BB_WITH_PO.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -511,20 +511,20 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Low Volume Season</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Urgent</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.8</v>
+        <v>1.14</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -568,20 +568,20 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Low Volume Season</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Urgent</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.16</v>
+        <v>0.97</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -625,20 +625,20 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Low Volume Season</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Urgent</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.85</v>
+        <v>0.97</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -682,20 +682,20 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Low Volume Season</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v/>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Urgent</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Low Volume Season</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Low Volume Season</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.93</v>
+        <v>0.84</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Low Volume Season</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Low Volume Season</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Low Volume Season</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.13</v>
+        <v>0.96</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Low Volume Season</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.89</v>
+        <v>1.15</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Low Volume Season</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.88</v>
+        <v>1.04</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Low Volume Season</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.93</v>
+        <v>1.15</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Low Volume Season</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.18</v>
+        <v>0.82</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Low Volume Season</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Low Volume Season</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Low Volume Season</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
